--- a/assets/ESR Formations-Prussia.xlsx
+++ b/assets/ESR Formations-Prussia.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9efa18f7c2e81ea4/Documents/NewRecruit/ESR/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="8_{4BA796EE-7FFE-4A21-8450-1F78C73A2E14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89A92DB9-379E-479A-AE57-892C149C2B06}"/>
+  <xr:revisionPtr revIDLastSave="37" documentId="8_{4BA796EE-7FFE-4A21-8450-1F78C73A2E14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E46D8E2-C3B3-4E0D-8EA4-85530167DB60}"/>
   <bookViews>
-    <workbookView xWindow="-26835" yWindow="540" windowWidth="26610" windowHeight="14595" activeTab="1" xr2:uid="{20271C60-C4FB-4B77-A1B3-909BAACA5FD5}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="26610" windowHeight="14595" activeTab="1" xr2:uid="{20271C60-C4FB-4B77-A1B3-909BAACA5FD5}"/>
   </bookViews>
   <sheets>
     <sheet name="BaselineFormations" sheetId="1" r:id="rId1"/>
     <sheet name="ExpandedFormations" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="FromArray_1">_xlfn.ANCHORARRAY(ExpandedFormations!$A$2)</definedName>
-    <definedName name="FromArray_3">_xlfn.ANCHORARRAY(ExpandedFormations!$D$2)</definedName>
+    <definedName name="FromArray_1">_xlfn.ANCHORARRAY(ExpandedFormations!$A$3)</definedName>
+    <definedName name="FromArray_3">_xlfn.ANCHORARRAY(ExpandedFormations!$D$3)</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="29">
   <si>
     <t>Formation</t>
   </si>
@@ -158,6 +158,12 @@
   </si>
   <si>
     <t>PR Kavallerie Division</t>
+  </si>
+  <si>
+    <t>PR Mixed</t>
+  </si>
+  <si>
+    <t>Mixed</t>
   </si>
 </sst>
 </file>
@@ -308,17 +314,17 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -335,6 +341,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -692,134 +702,134 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="13"/>
+      <c r="C2" s="15"/>
       <c r="D2" s="9"/>
       <c r="E2" s="2"/>
-      <c r="F2" s="13"/>
+      <c r="F2" s="15"/>
       <c r="I2" s="5"/>
       <c r="J2" s="5"/>
     </row>
     <row r="3" spans="1:10" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13"/>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
+      <c r="A3" s="15"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
       <c r="D3" s="9"/>
       <c r="E3" s="2"/>
-      <c r="F3" s="13"/>
-      <c r="I3" s="16" t="s">
+      <c r="F3" s="15"/>
+      <c r="I3" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="J3" s="15" t="s">
+      <c r="J3" s="13" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="13"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
+      <c r="A4" s="15"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
       <c r="D4" s="9"/>
       <c r="E4" s="2"/>
-      <c r="F4" s="13"/>
-      <c r="I4" s="16" t="s">
+      <c r="F4" s="15"/>
+      <c r="I4" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="J4" s="15" t="s">
+      <c r="J4" s="13" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="16" t="s">
         <v>8</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="3"/>
-      <c r="F5" s="14"/>
-      <c r="I5" s="16" t="s">
+      <c r="F5" s="16"/>
+      <c r="I5" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="J5" s="15" t="s">
+      <c r="J5" s="13" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="14"/>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
+      <c r="A6" s="16"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
       <c r="D6" s="10"/>
       <c r="E6" s="3"/>
-      <c r="F6" s="14"/>
-      <c r="I6" s="16" t="s">
+      <c r="F6" s="16"/>
+      <c r="I6" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="J6" s="15" t="s">
+      <c r="J6" s="13" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="I7" s="16" t="s">
+      <c r="I7" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="J7" s="15" t="s">
+      <c r="J7" s="13" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="I8" s="16" t="s">
+      <c r="I8" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="J8" s="15" t="s">
+      <c r="J8" s="13" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G9"/>
       <c r="H9"/>
-      <c r="I9" s="16" t="s">
+      <c r="I9" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="J9" s="15" t="s">
+      <c r="J9" s="13" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G10"/>
       <c r="H10"/>
-      <c r="I10" s="16" t="s">
+      <c r="I10" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="J10" s="16" t="s">
+      <c r="J10" s="14" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="G11"/>
       <c r="H11"/>
-      <c r="I11" s="16" t="s">
+      <c r="I11" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="J11" s="16" t="s">
+      <c r="J11" s="14" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G12"/>
       <c r="H12"/>
-      <c r="I12" s="16" t="s">
+      <c r="I12" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="J12" s="16" t="s">
+      <c r="J12" s="14" t="s">
         <v>10</v>
       </c>
     </row>
@@ -933,7 +943,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A52F401-E5BC-41DA-8596-65382229DEB1}">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40.5703125" customWidth="1"/>
@@ -989,59 +999,97 @@
         <v>PR Artillerie zu Pferd</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" t="str" cm="1">
-        <f t="array" ref="A2:C3">_xlfn.LET(_xlpm.data,_xlfn._xlws.FILTER(BaselineFormations!A:C,(BaselineFormations!A:A&lt;&gt;"Formation")*(NOT(ISBLANK(BaselineFormations!A:A)))),IF(_xlpm.data=0,"",_xlpm.data))</f>
+    <row r="2" spans="1:13" s="7" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="M2" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" t="str" cm="1">
+        <f t="array" ref="A3:C4">_xlfn.LET(_xlpm.data,_xlfn._xlws.FILTER(BaselineFormations!A:C,(BaselineFormations!A:A&lt;&gt;"Formation")*(NOT(ISBLANK(BaselineFormations!A:A)))),IF(_xlpm.data=0,"",_xlpm.data))</f>
         <v>PR Infanterie Division</v>
       </c>
-      <c r="B2" t="str">
+      <c r="B3" t="str">
         <v>Infantry</v>
       </c>
-      <c r="C2" t="str">
+      <c r="C3" t="str">
         <v/>
       </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="K2" t="s">
-        <v>12</v>
-      </c>
-      <c r="L2" t="s">
-        <v>12</v>
-      </c>
-      <c r="M2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" t="str">
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" t="str">
         <v>PR Kavallerie Division</v>
       </c>
-      <c r="B3" t="str">
+      <c r="B4" t="str">
         <v>Cavalry</v>
       </c>
-      <c r="C3" t="str">
+      <c r="C4" t="str">
         <v>Rapid Deployment</v>
       </c>
-      <c r="G3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I3" t="s">
-        <v>12</v>
-      </c>
-      <c r="J3" t="s">
-        <v>12</v>
-      </c>
-      <c r="L3" t="s">
+      <c r="G4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J4" t="s">
+        <v>12</v>
+      </c>
+      <c r="L4" t="s">
         <v>12</v>
       </c>
     </row>
